--- a/AAII_Financials/Quarterly/PRBKY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRBKY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>PRBKY</t>
   </si>
@@ -655,65 +655,68 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -744,8 +747,11 @@
       <c r="L8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -776,8 +782,11 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -808,8 +817,11 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -854,8 +867,11 @@
       <c r="L12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -886,8 +902,11 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -918,8 +937,11 @@
       <c r="L14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -950,8 +972,11 @@
       <c r="L15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -961,8 +986,9 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -993,8 +1019,11 @@
       <c r="L17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1025,8 +1054,11 @@
       <c r="L18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1039,8 +1071,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1071,8 +1104,11 @@
       <c r="L20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1103,8 +1139,11 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,8 +1174,11 @@
       <c r="L22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1167,8 +1209,11 @@
       <c r="L23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1199,8 +1244,11 @@
       <c r="L24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1231,8 +1279,11 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1263,8 +1314,11 @@
       <c r="L26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1295,8 +1349,11 @@
       <c r="L27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1327,8 +1384,11 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1359,8 +1419,11 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1391,8 +1454,11 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1423,8 +1489,11 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1455,8 +1524,11 @@
       <c r="L32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1487,8 +1559,11 @@
       <c r="L33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1519,8 +1594,11 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1551,45 +1629,51 @@
       <c r="L35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1602,8 +1686,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1616,296 +1701,324 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8873500</v>
+      </c>
+      <c r="E41" s="3">
         <v>6153600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8358600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9028500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7711100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5897100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7225400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11377400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9598200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12269900</v>
       </c>
     </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2885900</v>
+      </c>
+      <c r="E42" s="3">
         <v>2692300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5532500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1828000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1506800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1474300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2587200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1530200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1390800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1481300</v>
       </c>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2300900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2377500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>838300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1641400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1915400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1377000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>773400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>891100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>946100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>1298600</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="G44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J44" s="3">
         <v>1114000</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="K44" s="3" t="s">
         <v>4</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>627200</v>
+      </c>
+      <c r="E45" s="3">
         <v>638800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1821100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>667600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>815000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>653900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1568500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>161700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>236800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>413200</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15441600</v>
+      </c>
+      <c r="E46" s="3">
         <v>12616200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>19113500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13887100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>12634200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>10086500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14293400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14642000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>12813700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15658600</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>22626500</v>
+      </c>
+      <c r="E47" s="3">
         <v>22219500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>20833600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>21039500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>20891400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>18693300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>17383800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>17822900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>16501700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>15996300</v>
       </c>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1132200</v>
+      </c>
+      <c r="E48" s="3">
         <v>1095400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1126000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>956200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>884300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>798700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>781700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>849900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>856100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>788700</v>
       </c>
     </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>997400</v>
+      </c>
+      <c r="E49" s="3">
         <v>985800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>960400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>524500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>508500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>449600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>431700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>429400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>392200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>373300</v>
       </c>
     </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1936,8 +2049,11 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1968,40 +2084,46 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9818300</v>
+      </c>
+      <c r="E52" s="3">
         <v>9792500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7490900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5127300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5328200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4724400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2510600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5439400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5293000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5180700</v>
       </c>
     </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2032,40 +2154,46 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>107784800</v>
+      </c>
+      <c r="E54" s="3">
         <v>103792200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>106719500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>97452800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95418700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>85192400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>82869900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>87876400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82102200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83342300</v>
       </c>
     </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2078,8 +2206,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2092,200 +2221,219 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>78271400</v>
+      </c>
+      <c r="E57" s="3">
         <v>74859900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>77779700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>74863300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>73958900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>66470000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>65204500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>67576400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>64054400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>63254900</v>
       </c>
     </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5063400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4525500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4296100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3361500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2539000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2193000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2220700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3609200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3349400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6132300</v>
       </c>
     </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E59" s="3">
         <v>192600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>740900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>98600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>124500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>88600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>485600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>116000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>143600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>139200</v>
       </c>
     </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>83468500</v>
+      </c>
+      <c r="E60" s="3">
         <v>79578000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>83018700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>78323400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>76622400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>68751600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68037100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>71301600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>67547400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>69526400</v>
       </c>
     </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6876500</v>
+      </c>
+      <c r="E61" s="3">
         <v>6934200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7520300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6264200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6345300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5317800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5274900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5419400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4230200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3851500</v>
       </c>
     </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6061900</v>
+      </c>
+      <c r="E62" s="3">
         <v>5963300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4952400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2079100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1963600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1767200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>910000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1999800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1899700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1710000</v>
       </c>
     </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2316,8 +2464,11 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2348,8 +2499,11 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2380,40 +2534,46 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>96600000</v>
+      </c>
+      <c r="E66" s="3">
         <v>92669200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>95708600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>86744100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>85007600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>75910100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>74304800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78786500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>73740500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>75153700</v>
       </c>
     </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2426,8 +2586,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2458,8 +2619,11 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2490,8 +2654,11 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2522,8 +2689,11 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2554,40 +2724,46 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5279300</v>
+      </c>
+      <c r="E72" s="3">
         <v>5055900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4819800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>4694400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4388700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3772200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3318100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2847400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2921900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2699300</v>
       </c>
     </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2618,8 +2794,11 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2650,8 +2829,11 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2682,40 +2864,46 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11001900</v>
+      </c>
+      <c r="E76" s="3">
         <v>11030800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10918200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10616000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>10324100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>9205600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8507100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9008500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8301700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8129200</v>
       </c>
     </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2746,45 +2934,51 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
     </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -2815,8 +3009,11 @@
       <c r="L81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2829,40 +3026,44 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E83" s="3">
         <v>33500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>-36200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>-35400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>28600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>28400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28200</v>
       </c>
     </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2893,8 +3094,11 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2925,8 +3129,11 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2957,8 +3164,11 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2989,8 +3199,11 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3021,40 +3234,46 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-449000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2281800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1022700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>316800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-458000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-229100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4660900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-447200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4568700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1971100</v>
       </c>
     </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3067,40 +3286,44 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-64600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-34000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-43200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-134600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-32300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-46100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28100</v>
       </c>
     </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3131,8 +3354,11 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3163,40 +3389,46 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-466100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-426600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-931100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-38700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-285400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-749000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-129400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>117100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>352500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>183400</v>
       </c>
     </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3209,8 +3441,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3241,8 +3474,11 @@
       <c r="L96" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3273,8 +3509,11 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3305,8 +3544,11 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3337,100 +3579,112 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3683300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1856300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3831200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1050100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2085700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1706700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2449500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1744400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1607200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-927800</v>
       </c>
     </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-37600</v>
+      </c>
+      <c r="E101" s="3">
         <v>1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-27900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>20400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-18000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-19700</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2778500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4561300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1873900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1324700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1304800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2683700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2341900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1386300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2588700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1222400</v>
       </c>
     </row>
